--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/28,07,26 Останкино СЫРЫ/дв 28,07,26 днрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/28,07,26 Останкино СЫРЫ/дв 28,07,26 днрсч ост сыр.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\07,26\28,07,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0858030-DD8D-4166-B0A3-33A15C5CBCF7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B8A0C1-6B88-44F5-A455-8E276184A9F3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -268,12 +268,6 @@
     <t>нужно увеличить продажи</t>
   </si>
   <si>
-    <t>62шт в уценку (28,07,26)</t>
-  </si>
-  <si>
-    <t>34шт в уценку (28,07,26)</t>
-  </si>
-  <si>
     <t>ТК</t>
   </si>
   <si>
@@ -296,6 +290,12 @@
   </si>
   <si>
     <t>03,08,</t>
+  </si>
+  <si>
+    <t>30,07,26 - нет на заводе / 62шт в уценку (28,07,26)</t>
+  </si>
+  <si>
+    <t>30,07,26 - нет на заводе / 34шт в уценку (28,07,26)</t>
   </si>
 </sst>
 </file>
@@ -349,7 +349,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,6 +375,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -414,7 +420,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -424,7 +430,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
@@ -432,6 +437,8 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -750,7 +757,7 @@
     <col min="13" max="14" width="0.5703125" customWidth="1"/>
     <col min="15" max="15" width="0.28515625" customWidth="1"/>
     <col min="16" max="18" width="7" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" style="16" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" style="15" customWidth="1"/>
     <col min="20" max="21" width="5" customWidth="1"/>
     <col min="22" max="30" width="6" customWidth="1"/>
     <col min="31" max="31" width="49.42578125" customWidth="1"/>
@@ -914,13 +921,13 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>16</v>
@@ -1004,7 +1011,7 @@
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -1019,7 +1026,7 @@
         <v>25</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Z4" s="1" t="s">
         <v>26</v>
@@ -1105,7 +1112,7 @@
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>4183</v>
+        <v>4135</v>
       </c>
       <c r="S5" s="4"/>
       <c r="T5" s="1"/>
@@ -1216,7 +1223,7 @@
         <f>VLOOKUP(A6,заказ!A:B,2,0)</f>
         <v>48</v>
       </c>
-      <c r="S6" s="14"/>
+      <c r="S6" s="13"/>
       <c r="T6" s="1">
         <f>(F6+Q6)/P6</f>
         <v>20</v>
@@ -1324,7 +1331,7 @@
         <f>VLOOKUP(A7,заказ!A:B,2,0)</f>
         <v>24</v>
       </c>
-      <c r="S7" s="14"/>
+      <c r="S7" s="13"/>
       <c r="T7" s="1">
         <f t="shared" ref="T7:T47" si="6">(F7+Q7)/P7</f>
         <v>20</v>
@@ -1432,7 +1439,7 @@
         <f>VLOOKUP(A8,заказ!A:B,2,0)</f>
         <v>24</v>
       </c>
-      <c r="S8" s="14"/>
+      <c r="S8" s="13"/>
       <c r="T8" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -1540,7 +1547,7 @@
         <f>VLOOKUP(A9,заказ!A:B,2,0)</f>
         <v>100</v>
       </c>
-      <c r="S9" s="14"/>
+      <c r="S9" s="13"/>
       <c r="T9" s="1">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -1640,11 +1647,10 @@
         <f>10*P10-F10</f>
         <v>20</v>
       </c>
-      <c r="R10" s="5">
-        <f>VLOOKUP(A10,заказ!A:B,2,0)</f>
-        <v>24</v>
-      </c>
-      <c r="S10" s="14"/>
+      <c r="R10" s="16">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13"/>
       <c r="T10" s="1">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -1680,8 +1686,8 @@
       <c r="AD10" s="1">
         <v>2.4</v>
       </c>
-      <c r="AE10" s="9" t="s">
-        <v>78</v>
+      <c r="AE10" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="AF10" s="1">
         <f t="shared" si="3"/>
@@ -1746,11 +1752,10 @@
         <f>10*P11-F11</f>
         <v>30</v>
       </c>
-      <c r="R11" s="5">
-        <f>VLOOKUP(A11,заказ!A:B,2,0)</f>
-        <v>24</v>
-      </c>
-      <c r="S11" s="14"/>
+      <c r="R11" s="16">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13"/>
       <c r="T11" s="1">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -1786,8 +1791,8 @@
       <c r="AD11" s="1">
         <v>1.4</v>
       </c>
-      <c r="AE11" s="9" t="s">
-        <v>79</v>
+      <c r="AE11" s="17" t="s">
+        <v>87</v>
       </c>
       <c r="AF11" s="1">
         <f t="shared" si="3"/>
@@ -1854,7 +1859,7 @@
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
-      <c r="S12" s="14"/>
+      <c r="S12" s="13"/>
       <c r="T12" s="1">
         <f t="shared" si="6"/>
         <v>55.81609195402298</v>
@@ -1890,7 +1895,7 @@
       <c r="AD12" s="1">
         <v>0</v>
       </c>
-      <c r="AE12" s="11" t="s">
+      <c r="AE12" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF12" s="1">
@@ -1958,7 +1963,7 @@
       </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
-      <c r="S13" s="14"/>
+      <c r="S13" s="13"/>
       <c r="T13" s="1">
         <f t="shared" si="6"/>
         <v>236.66666666666669</v>
@@ -1994,7 +1999,7 @@
       <c r="AD13" s="1">
         <v>0</v>
       </c>
-      <c r="AE13" s="11" t="s">
+      <c r="AE13" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF13" s="1">
@@ -2022,7 +2027,7 @@
       <c r="AY13" s="1"/>
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -2069,8 +2074,8 @@
         <f>VLOOKUP(A14,заказ!A:B,2,0)</f>
         <v>84</v>
       </c>
-      <c r="S14" s="15" t="s">
-        <v>82</v>
+      <c r="S14" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" si="6"/>
@@ -2107,7 +2112,7 @@
       <c r="AD14" s="1">
         <v>19.600000000000001</v>
       </c>
-      <c r="AE14" s="11" t="s">
+      <c r="AE14" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF14" s="1">
@@ -2175,7 +2180,7 @@
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
-      <c r="S15" s="14"/>
+      <c r="S15" s="13"/>
       <c r="T15" s="1">
         <f t="shared" si="6"/>
         <v>91.25</v>
@@ -2211,7 +2216,7 @@
       <c r="AD15" s="1">
         <v>5</v>
       </c>
-      <c r="AE15" s="11" t="s">
+      <c r="AE15" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF15" s="1">
@@ -2281,7 +2286,7 @@
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
-      <c r="S16" s="14"/>
+      <c r="S16" s="13"/>
       <c r="T16" s="1">
         <f t="shared" si="6"/>
         <v>39.746835443037973</v>
@@ -2317,7 +2322,7 @@
       <c r="AD16" s="1">
         <v>60.6</v>
       </c>
-      <c r="AE16" s="11" t="s">
+      <c r="AE16" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF16" s="1">
@@ -2387,7 +2392,7 @@
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
-      <c r="S17" s="14"/>
+      <c r="S17" s="13"/>
       <c r="T17" s="1">
         <f t="shared" si="6"/>
         <v>101.66666666666666</v>
@@ -2423,7 +2428,7 @@
       <c r="AD17" s="1">
         <v>13.2</v>
       </c>
-      <c r="AE17" s="11" t="s">
+      <c r="AE17" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF17" s="1">
@@ -2493,7 +2498,7 @@
       </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
-      <c r="S18" s="14"/>
+      <c r="S18" s="13"/>
       <c r="T18" s="1">
         <f t="shared" si="6"/>
         <v>19.545454545454543</v>
@@ -2602,7 +2607,7 @@
         <f>VLOOKUP(A19,заказ!A:B,2,0)</f>
         <v>16</v>
       </c>
-      <c r="S19" s="14"/>
+      <c r="S19" s="13"/>
       <c r="T19" s="1">
         <f t="shared" si="6"/>
         <v>20.68181818181818</v>
@@ -2706,7 +2711,7 @@
       </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
-      <c r="S20" s="14"/>
+      <c r="S20" s="13"/>
       <c r="T20" s="1">
         <f t="shared" si="6"/>
         <v>22.793661981196056</v>
@@ -2742,7 +2747,7 @@
       <c r="AD20" s="1">
         <v>33.200000000000003</v>
       </c>
-      <c r="AE20" s="10" t="s">
+      <c r="AE20" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AF20" s="1">
@@ -2812,7 +2817,7 @@
       </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
-      <c r="S21" s="14"/>
+      <c r="S21" s="13"/>
       <c r="T21" s="1">
         <f t="shared" si="6"/>
         <v>24.62962962962963</v>
@@ -2848,7 +2853,7 @@
       <c r="AD21" s="1">
         <v>28.8</v>
       </c>
-      <c r="AE21" s="10" t="s">
+      <c r="AE21" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AF21" s="1">
@@ -2914,7 +2919,7 @@
       </c>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
-      <c r="S22" s="14"/>
+      <c r="S22" s="13"/>
       <c r="T22" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -2950,7 +2955,7 @@
       <c r="AD22" s="1">
         <v>3.2</v>
       </c>
-      <c r="AE22" s="11" t="s">
+      <c r="AE22" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF22" s="1">
@@ -3018,7 +3023,7 @@
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
-      <c r="S23" s="14"/>
+      <c r="S23" s="13"/>
       <c r="T23" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -3054,7 +3059,7 @@
       <c r="AD23" s="1">
         <v>0.6</v>
       </c>
-      <c r="AE23" s="11" t="s">
+      <c r="AE23" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF23" s="1">
@@ -3130,7 +3135,7 @@
         <f>VLOOKUP(A24,заказ!A:B,2,0)</f>
         <v>66</v>
       </c>
-      <c r="S24" s="14"/>
+      <c r="S24" s="13"/>
       <c r="T24" s="1">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -3240,7 +3245,7 @@
         <f>VLOOKUP(A25,заказ!A:B,2,0)</f>
         <v>232</v>
       </c>
-      <c r="S25" s="14"/>
+      <c r="S25" s="13"/>
       <c r="T25" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -3348,7 +3353,7 @@
         <f>VLOOKUP(A26,заказ!A:B,2,0)</f>
         <v>40</v>
       </c>
-      <c r="S26" s="14"/>
+      <c r="S26" s="13"/>
       <c r="T26" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -3456,7 +3461,7 @@
         <f>VLOOKUP(A27,заказ!A:B,2,0)</f>
         <v>120</v>
       </c>
-      <c r="S27" s="14"/>
+      <c r="S27" s="13"/>
       <c r="T27" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -3560,7 +3565,7 @@
       </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
-      <c r="S28" s="14"/>
+      <c r="S28" s="13"/>
       <c r="T28" s="1">
         <f t="shared" si="6"/>
         <v>89.42307692307692</v>
@@ -3596,7 +3601,7 @@
       <c r="AD28" s="1">
         <v>11.6</v>
       </c>
-      <c r="AE28" s="11" t="s">
+      <c r="AE28" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF28" s="1">
@@ -3672,7 +3677,7 @@
         <f>VLOOKUP(A29,заказ!A:B,2,0)</f>
         <v>830</v>
       </c>
-      <c r="S29" s="14"/>
+      <c r="S29" s="13"/>
       <c r="T29" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -3776,7 +3781,7 @@
       </c>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
-      <c r="S30" s="14"/>
+      <c r="S30" s="13"/>
       <c r="T30" s="1">
         <f t="shared" si="6"/>
         <v>80.434782608695656</v>
@@ -3812,7 +3817,7 @@
       <c r="AD30" s="1">
         <v>6</v>
       </c>
-      <c r="AE30" s="11" t="s">
+      <c r="AE30" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF30" s="1">
@@ -3882,7 +3887,7 @@
       </c>
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
-      <c r="S31" s="14"/>
+      <c r="S31" s="13"/>
       <c r="T31" s="1">
         <f t="shared" si="6"/>
         <v>65.384615384615387</v>
@@ -3918,7 +3923,7 @@
       <c r="AD31" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AE31" s="11" t="s">
+      <c r="AE31" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF31" s="1">
@@ -3994,7 +3999,7 @@
         <f>VLOOKUP(A32,заказ!A:B,2,0)</f>
         <v>1200</v>
       </c>
-      <c r="S32" s="14"/>
+      <c r="S32" s="13"/>
       <c r="T32" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -4056,7 +4061,7 @@
       <c r="AY32" s="1"/>
     </row>
     <row r="33" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -4096,15 +4101,15 @@
         <f t="shared" si="4"/>
         <v>5.4</v>
       </c>
-      <c r="Q33" s="13">
+      <c r="Q33" s="12">
         <v>300</v>
       </c>
       <c r="R33" s="5">
         <f>VLOOKUP(A33,заказ!A:B,2,0)</f>
         <v>300</v>
       </c>
-      <c r="S33" s="15" t="s">
-        <v>81</v>
+      <c r="S33" s="14" t="s">
+        <v>79</v>
       </c>
       <c r="T33" s="1">
         <f t="shared" si="6"/>
@@ -4141,7 +4146,7 @@
       <c r="AD33" s="1">
         <v>9.8000000000000007</v>
       </c>
-      <c r="AE33" s="11" t="s">
+      <c r="AE33" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF33" s="1">
@@ -4216,7 +4221,7 @@
         <f>VLOOKUP(A34,заказ!A:B,2,0)</f>
         <v>16</v>
       </c>
-      <c r="S34" s="14"/>
+      <c r="S34" s="13"/>
       <c r="T34" s="1">
         <f t="shared" si="6"/>
         <v>18.333333333333332</v>
@@ -4326,7 +4331,7 @@
         <f>VLOOKUP(A35,заказ!A:B,2,0)</f>
         <v>64</v>
       </c>
-      <c r="S35" s="14"/>
+      <c r="S35" s="13"/>
       <c r="T35" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -4426,7 +4431,7 @@
       </c>
       <c r="Q36" s="5"/>
       <c r="R36" s="5"/>
-      <c r="S36" s="14"/>
+      <c r="S36" s="13"/>
       <c r="T36" s="1">
         <f t="shared" si="6"/>
         <v>44.891607308764321</v>
@@ -4462,7 +4467,7 @@
       <c r="AD36" s="1">
         <v>4.3655999999999997</v>
       </c>
-      <c r="AE36" s="11" t="s">
+      <c r="AE36" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF36" s="1">
@@ -4535,7 +4540,7 @@
         <f>VLOOKUP(A37,заказ!A:B,2,0)</f>
         <v>16</v>
       </c>
-      <c r="S37" s="14"/>
+      <c r="S37" s="13"/>
       <c r="T37" s="1">
         <f t="shared" si="6"/>
         <v>17.344279661016948</v>
@@ -4645,7 +4650,7 @@
         <f>VLOOKUP(A38,заказ!A:B,2,0)</f>
         <v>66</v>
       </c>
-      <c r="S38" s="14"/>
+      <c r="S38" s="13"/>
       <c r="T38" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -4745,7 +4750,7 @@
       </c>
       <c r="Q39" s="5"/>
       <c r="R39" s="5"/>
-      <c r="S39" s="14"/>
+      <c r="S39" s="13"/>
       <c r="T39" s="1">
         <f t="shared" si="6"/>
         <v>50.088938714499257</v>
@@ -4781,7 +4786,7 @@
       <c r="AD39" s="1">
         <v>0.48559999999999998</v>
       </c>
-      <c r="AE39" s="11" t="s">
+      <c r="AE39" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF39" s="1">
@@ -4809,7 +4814,7 @@
       <c r="AY39" s="1"/>
     </row>
     <row r="40" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="11" t="s">
         <v>69</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -4843,7 +4848,7 @@
         <f t="shared" si="4"/>
         <v>-0.4</v>
       </c>
-      <c r="Q40" s="13">
+      <c r="Q40" s="12">
         <f>200+100</f>
         <v>300</v>
       </c>
@@ -4851,8 +4856,8 @@
         <f>VLOOKUP(A40,заказ!A:B,2,0)</f>
         <v>300</v>
       </c>
-      <c r="S40" s="15" t="s">
-        <v>83</v>
+      <c r="S40" s="14" t="s">
+        <v>81</v>
       </c>
       <c r="T40" s="1">
         <f t="shared" si="6"/>
@@ -4963,7 +4968,7 @@
         <f>VLOOKUP(A41,заказ!A:B,2,0)</f>
         <v>402</v>
       </c>
-      <c r="S41" s="14"/>
+      <c r="S41" s="13"/>
       <c r="T41" s="1">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -5061,7 +5066,7 @@
       </c>
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
-      <c r="S42" s="14"/>
+      <c r="S42" s="13"/>
       <c r="T42" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -5171,7 +5176,7 @@
         <f>VLOOKUP(A43,заказ!A:B,2,0)</f>
         <v>112</v>
       </c>
-      <c r="S43" s="14"/>
+      <c r="S43" s="13"/>
       <c r="T43" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -5271,7 +5276,7 @@
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
-      <c r="S44" s="14"/>
+      <c r="S44" s="13"/>
       <c r="T44" s="1">
         <f t="shared" si="6"/>
         <v>155</v>
@@ -5307,7 +5312,7 @@
       <c r="AD44" s="1">
         <v>15.2</v>
       </c>
-      <c r="AE44" s="11" t="s">
+      <c r="AE44" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF44" s="1">
@@ -5369,7 +5374,7 @@
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
-      <c r="S45" s="14"/>
+      <c r="S45" s="13"/>
       <c r="T45" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -5405,7 +5410,7 @@
       <c r="AD45" s="1">
         <v>1.8675999999999999</v>
       </c>
-      <c r="AE45" s="11" t="s">
+      <c r="AE45" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF45" s="1">
@@ -5471,7 +5476,7 @@
       </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
-      <c r="S46" s="14"/>
+      <c r="S46" s="13"/>
       <c r="T46" s="1">
         <f t="shared" si="6"/>
         <v>76.428571428571431</v>
@@ -5507,7 +5512,7 @@
       <c r="AD46" s="1">
         <v>10.8</v>
       </c>
-      <c r="AE46" s="11" t="s">
+      <c r="AE46" s="10" t="s">
         <v>38</v>
       </c>
       <c r="AF46" s="1">
@@ -5579,7 +5584,7 @@
         <f>VLOOKUP(A47,заказ!A:B,2,0)</f>
         <v>75</v>
       </c>
-      <c r="S47" s="14"/>
+      <c r="S47" s="13"/>
       <c r="T47" s="1">
         <f t="shared" si="6"/>
         <v>18</v>
